--- a/ro-crate-validation.xlsx
+++ b/ro-crate-validation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alvinsw/uqslc/codes/corpus-tools-cooee/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E6AB865-1257-AA40-B70D-4AE4ABE89ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{699280FE-78C4-6E4C-A659-C54E7142A8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1740" yWindow="1680" windowWidth="27240" windowHeight="16420" activeTab="1" xr2:uid="{756E4AC4-F825-4F44-B76C-9C1C961306D6}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="types" sheetId="1" r:id="rId1"/>
     <sheet name="properties" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -487,7 +487,7 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -542,7 +542,7 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>2713</v>
+        <v>2709</v>
       </c>
     </row>
   </sheetData>

--- a/ro-crate-validation.xlsx
+++ b/ro-crate-validation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alvinsw/uqslc/codes/corpus-tools-cooee/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cjhaseloff/Documents/GitHub/LDaCA/corpus-tools-cooee/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{699280FE-78C4-6E4C-A659-C54E7142A8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA0B1816-71EA-4E41-9C88-E09047F684EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1740" yWindow="1680" windowWidth="27240" windowHeight="16420" activeTab="1" xr2:uid="{756E4AC4-F825-4F44-B76C-9C1C961306D6}"/>
+    <workbookView xWindow="1160" yWindow="1100" windowWidth="27240" windowHeight="16420" activeTab="1" xr2:uid="{756E4AC4-F825-4F44-B76C-9C1C961306D6}"/>
   </bookViews>
   <sheets>
     <sheet name="types" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>type</t>
   </si>
@@ -48,18 +48,9 @@
     <t>File</t>
   </si>
   <si>
-    <t>Person</t>
-  </si>
-  <si>
     <t>property</t>
   </si>
   <si>
-    <t>hasPart</t>
-  </si>
-  <si>
-    <t>./</t>
-  </si>
-  <si>
     <t>value</t>
   </si>
   <si>
@@ -70,9 +61,6 @@
   </si>
   <si>
     <t>crate</t>
-  </si>
-  <si>
-    <t>Place</t>
   </si>
   <si>
     <t>entity</t>
@@ -448,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AB1F507-EA73-9344-9364-A6096358D74D}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18.5" bestFit="1" customWidth="1"/>
@@ -457,7 +445,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -476,7 +464,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -484,26 +472,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>1357</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>1904</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6">
-        <v>27</v>
+        <v>1354</v>
       </c>
     </row>
   </sheetData>
@@ -514,7 +486,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F6AA071-2F0F-0743-BFA5-7EAF4447793A}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.83203125" customWidth="1"/>
@@ -522,27 +494,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>2709</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/ro-crate-validation.xlsx
+++ b/ro-crate-validation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cjhaseloff/Documents/GitHub/LDaCA/corpus-tools-cooee/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alvinsw/uqslc/codes/corpus-tools-cooee/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA0B1816-71EA-4E41-9C88-E09047F684EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FF5034D-1934-6049-9522-9F2A10FCD8DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1160" yWindow="1100" windowWidth="27240" windowHeight="16420" activeTab="1" xr2:uid="{756E4AC4-F825-4F44-B76C-9C1C961306D6}"/>
+    <workbookView xWindow="1160" yWindow="1100" windowWidth="27240" windowHeight="16420" xr2:uid="{756E4AC4-F825-4F44-B76C-9C1C961306D6}"/>
   </bookViews>
   <sheets>
     <sheet name="types" sheetId="1" r:id="rId1"/>
@@ -459,7 +459,7 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>2713</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
